--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119830743</v>
+        <v>119830737</v>
       </c>
       <c r="B2" t="n">
-        <v>90067</v>
+        <v>91834</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424092</v>
+        <v>423946</v>
       </c>
       <c r="R2" t="n">
-        <v>6919785</v>
+        <v>6919903</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119830771</v>
+        <v>119830755</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>91828</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423911</v>
+        <v>424017</v>
       </c>
       <c r="R3" t="n">
-        <v>6920075</v>
+        <v>6919755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119830751</v>
+        <v>119830770</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>424052</v>
+        <v>423909</v>
       </c>
       <c r="R4" t="n">
-        <v>6919686</v>
+        <v>6920068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119830756</v>
+        <v>119830752</v>
       </c>
       <c r="B5" t="n">
-        <v>91863</v>
+        <v>88153</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>424010</v>
+        <v>424027</v>
       </c>
       <c r="R5" t="n">
-        <v>6919761</v>
+        <v>6919739</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119830735</v>
+        <v>119830756</v>
       </c>
       <c r="B6" t="n">
-        <v>89252</v>
+        <v>91863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>424039</v>
+        <v>424010</v>
       </c>
       <c r="R6" t="n">
-        <v>6919773</v>
+        <v>6919761</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119830759</v>
+        <v>119830738</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>423934</v>
+        <v>423951</v>
       </c>
       <c r="R7" t="n">
-        <v>6920034</v>
+        <v>6919904</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119830770</v>
+        <v>119830751</v>
       </c>
       <c r="B8" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>423909</v>
+        <v>424052</v>
       </c>
       <c r="R8" t="n">
-        <v>6920068</v>
+        <v>6919686</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119830766</v>
+        <v>119830734</v>
       </c>
       <c r="B9" t="n">
         <v>91834</v>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>423930</v>
+        <v>423957</v>
       </c>
       <c r="R9" t="n">
-        <v>6920043</v>
+        <v>6919904</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119830767</v>
+        <v>119830768</v>
       </c>
       <c r="B10" t="n">
-        <v>89275</v>
+        <v>89252</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>423917</v>
+        <v>423899</v>
       </c>
       <c r="R10" t="n">
-        <v>6920047</v>
+        <v>6920037</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119830744</v>
+        <v>119830754</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>424066</v>
+        <v>424024</v>
       </c>
       <c r="R11" t="n">
-        <v>6919837</v>
+        <v>6919740</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119830739</v>
+        <v>119830769</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>423961</v>
+        <v>423912</v>
       </c>
       <c r="R12" t="n">
-        <v>6919906</v>
+        <v>6920047</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119830738</v>
+        <v>119830735</v>
       </c>
       <c r="B13" t="n">
-        <v>91852</v>
+        <v>89252</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>423951</v>
+        <v>424039</v>
       </c>
       <c r="R13" t="n">
-        <v>6919904</v>
+        <v>6919773</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119830763</v>
+        <v>119830762</v>
       </c>
       <c r="B14" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>424010</v>
+        <v>424025</v>
       </c>
       <c r="R14" t="n">
-        <v>6919840</v>
+        <v>6919826</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119830769</v>
+        <v>119830771</v>
       </c>
       <c r="B15" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>423912</v>
+        <v>423911</v>
       </c>
       <c r="R15" t="n">
-        <v>6920047</v>
+        <v>6920075</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119830762</v>
+        <v>119830766</v>
       </c>
       <c r="B16" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>424025</v>
+        <v>423930</v>
       </c>
       <c r="R16" t="n">
-        <v>6919826</v>
+        <v>6920043</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119830752</v>
+        <v>119830744</v>
       </c>
       <c r="B17" t="n">
-        <v>88153</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>424027</v>
+        <v>424066</v>
       </c>
       <c r="R17" t="n">
-        <v>6919739</v>
+        <v>6919837</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119830764</v>
+        <v>119830760</v>
       </c>
       <c r="B18" t="n">
-        <v>90582</v>
+        <v>89252</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>6276</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>424000</v>
+        <v>424023</v>
       </c>
       <c r="R18" t="n">
-        <v>6919867</v>
+        <v>6919928</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119830737</v>
+        <v>119830765</v>
       </c>
       <c r="B19" t="n">
         <v>91834</v>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>423946</v>
+        <v>424019</v>
       </c>
       <c r="R19" t="n">
-        <v>6919903</v>
+        <v>6919898</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119830736</v>
+        <v>119830733</v>
       </c>
       <c r="B20" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423894</v>
+        <v>423939</v>
       </c>
       <c r="R20" t="n">
-        <v>6920052</v>
+        <v>6919929</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119830754</v>
+        <v>119830739</v>
       </c>
       <c r="B21" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>424024</v>
+        <v>423961</v>
       </c>
       <c r="R21" t="n">
-        <v>6919740</v>
+        <v>6919906</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830733</v>
+        <v>119830743</v>
       </c>
       <c r="B22" t="n">
-        <v>89252</v>
+        <v>90067</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6276</v>
+        <v>256703</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423939</v>
+        <v>424092</v>
       </c>
       <c r="R22" t="n">
-        <v>6919929</v>
+        <v>6919785</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,7 +2901,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830734</v>
+        <v>119830736</v>
       </c>
       <c r="B23" t="n">
         <v>91834</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>423957</v>
+        <v>423894</v>
       </c>
       <c r="R23" t="n">
-        <v>6919904</v>
+        <v>6920052</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119830753</v>
+        <v>119830767</v>
       </c>
       <c r="B24" t="n">
-        <v>91863</v>
+        <v>89275</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,25 +3019,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>6286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>424027</v>
+        <v>423917</v>
       </c>
       <c r="R24" t="n">
-        <v>6919739</v>
+        <v>6920047</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119830768</v>
+        <v>119830761</v>
       </c>
       <c r="B25" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3125,25 +3125,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>423899</v>
+        <v>424024</v>
       </c>
       <c r="R25" t="n">
-        <v>6920037</v>
+        <v>6919805</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119830760</v>
+        <v>119830753</v>
       </c>
       <c r="B26" t="n">
-        <v>89252</v>
+        <v>91863</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6276</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>424023</v>
+        <v>424027</v>
       </c>
       <c r="R26" t="n">
-        <v>6919928</v>
+        <v>6919739</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119830765</v>
+        <v>119830759</v>
       </c>
       <c r="B27" t="n">
         <v>91834</v>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>424019</v>
+        <v>423934</v>
       </c>
       <c r="R27" t="n">
-        <v>6919898</v>
+        <v>6920034</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119830761</v>
+        <v>119830763</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3443,25 +3443,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>424024</v>
+        <v>424010</v>
       </c>
       <c r="R28" t="n">
-        <v>6919805</v>
+        <v>6919840</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119830755</v>
+        <v>119830764</v>
       </c>
       <c r="B29" t="n">
-        <v>91828</v>
+        <v>90582</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3549,25 +3549,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>149</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424017</v>
+        <v>424000</v>
       </c>
       <c r="R29" t="n">
-        <v>6919755</v>
+        <v>6919867</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119830751</v>
+        <v>119830768</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>89252</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>424052</v>
+        <v>423899</v>
       </c>
       <c r="R8" t="n">
-        <v>6919686</v>
+        <v>6920037</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119830734</v>
+        <v>119830751</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>423957</v>
+        <v>424052</v>
       </c>
       <c r="R9" t="n">
-        <v>6919904</v>
+        <v>6919686</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119830768</v>
+        <v>119830734</v>
       </c>
       <c r="B10" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>423899</v>
+        <v>423957</v>
       </c>
       <c r="R10" t="n">
-        <v>6920037</v>
+        <v>6919904</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830743</v>
+        <v>119830736</v>
       </c>
       <c r="B22" t="n">
-        <v>90067</v>
+        <v>91834</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>424092</v>
+        <v>423894</v>
       </c>
       <c r="R22" t="n">
-        <v>6919785</v>
+        <v>6920052</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830736</v>
+        <v>119830743</v>
       </c>
       <c r="B23" t="n">
-        <v>91834</v>
+        <v>90067</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2913,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>423894</v>
+        <v>424092</v>
       </c>
       <c r="R23" t="n">
-        <v>6920052</v>
+        <v>6919785</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119830737</v>
+        <v>119830756</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>91863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>423946</v>
+        <v>424010</v>
       </c>
       <c r="R2" t="n">
-        <v>6919903</v>
+        <v>6919761</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119830755</v>
+        <v>119830736</v>
       </c>
       <c r="B3" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424017</v>
+        <v>423894</v>
       </c>
       <c r="R3" t="n">
-        <v>6919755</v>
+        <v>6920052</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119830770</v>
+        <v>119830759</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423909</v>
+        <v>423934</v>
       </c>
       <c r="R4" t="n">
-        <v>6920068</v>
+        <v>6920034</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119830752</v>
+        <v>119830734</v>
       </c>
       <c r="B5" t="n">
-        <v>88153</v>
+        <v>91834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4962</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>424027</v>
+        <v>423957</v>
       </c>
       <c r="R5" t="n">
-        <v>6919739</v>
+        <v>6919904</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119830756</v>
+        <v>119830763</v>
       </c>
       <c r="B6" t="n">
-        <v>91863</v>
+        <v>91884</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,7 +1142,7 @@
         <v>424010</v>
       </c>
       <c r="R6" t="n">
-        <v>6919761</v>
+        <v>6919840</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119830738</v>
+        <v>119830764</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>90582</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>423951</v>
+        <v>424000</v>
       </c>
       <c r="R7" t="n">
-        <v>6919904</v>
+        <v>6919867</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119830768</v>
+        <v>119830733</v>
       </c>
       <c r="B8" t="n">
         <v>89252</v>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>423899</v>
+        <v>423939</v>
       </c>
       <c r="R8" t="n">
-        <v>6920037</v>
+        <v>6919929</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119830751</v>
+        <v>119830760</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>89252</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>424052</v>
+        <v>424023</v>
       </c>
       <c r="R9" t="n">
-        <v>6919686</v>
+        <v>6919928</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119830734</v>
+        <v>119830765</v>
       </c>
       <c r="B10" t="n">
         <v>91834</v>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>423957</v>
+        <v>424019</v>
       </c>
       <c r="R10" t="n">
-        <v>6919904</v>
+        <v>6919898</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119830754</v>
+        <v>119830766</v>
       </c>
       <c r="B11" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>424024</v>
+        <v>423930</v>
       </c>
       <c r="R11" t="n">
-        <v>6919740</v>
+        <v>6920043</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119830769</v>
+        <v>119830754</v>
       </c>
       <c r="B12" t="n">
-        <v>89252</v>
+        <v>91832</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>423912</v>
+        <v>424024</v>
       </c>
       <c r="R12" t="n">
-        <v>6920047</v>
+        <v>6919740</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119830762</v>
+        <v>119830767</v>
       </c>
       <c r="B14" t="n">
-        <v>91856</v>
+        <v>89275</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>424025</v>
+        <v>423917</v>
       </c>
       <c r="R14" t="n">
-        <v>6919826</v>
+        <v>6920047</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119830771</v>
+        <v>119830743</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
+        <v>90067</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>423911</v>
+        <v>424092</v>
       </c>
       <c r="R15" t="n">
-        <v>6920075</v>
+        <v>6919785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119830766</v>
+        <v>119830744</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>423930</v>
+        <v>424066</v>
       </c>
       <c r="R16" t="n">
-        <v>6920043</v>
+        <v>6919837</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119830744</v>
+        <v>119830738</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>424066</v>
+        <v>423951</v>
       </c>
       <c r="R17" t="n">
-        <v>6919837</v>
+        <v>6919904</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119830760</v>
+        <v>119830739</v>
       </c>
       <c r="B18" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>424023</v>
+        <v>423961</v>
       </c>
       <c r="R18" t="n">
-        <v>6919928</v>
+        <v>6919906</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119830765</v>
+        <v>119830752</v>
       </c>
       <c r="B19" t="n">
-        <v>91834</v>
+        <v>88153</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>4962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>424019</v>
+        <v>424027</v>
       </c>
       <c r="R19" t="n">
-        <v>6919898</v>
+        <v>6919739</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119830733</v>
+        <v>119830762</v>
       </c>
       <c r="B20" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423939</v>
+        <v>424025</v>
       </c>
       <c r="R20" t="n">
-        <v>6919929</v>
+        <v>6919826</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119830739</v>
+        <v>119830751</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2701,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423961</v>
+        <v>424052</v>
       </c>
       <c r="R21" t="n">
-        <v>6919906</v>
+        <v>6919686</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830736</v>
+        <v>119830761</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423894</v>
+        <v>424024</v>
       </c>
       <c r="R22" t="n">
-        <v>6920052</v>
+        <v>6919805</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830743</v>
+        <v>119830737</v>
       </c>
       <c r="B23" t="n">
-        <v>90067</v>
+        <v>91834</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2913,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>424092</v>
+        <v>423946</v>
       </c>
       <c r="R23" t="n">
-        <v>6919785</v>
+        <v>6919903</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119830767</v>
+        <v>119830770</v>
       </c>
       <c r="B24" t="n">
-        <v>89275</v>
+        <v>91832</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,25 +3019,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>423917</v>
+        <v>423909</v>
       </c>
       <c r="R24" t="n">
-        <v>6920047</v>
+        <v>6920068</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119830761</v>
+        <v>119830768</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3125,25 +3125,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>424024</v>
+        <v>423899</v>
       </c>
       <c r="R25" t="n">
-        <v>6919805</v>
+        <v>6920037</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119830759</v>
+        <v>119830771</v>
       </c>
       <c r="B27" t="n">
         <v>91834</v>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>423934</v>
+        <v>423911</v>
       </c>
       <c r="R27" t="n">
-        <v>6920034</v>
+        <v>6920075</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119830763</v>
+        <v>119830769</v>
       </c>
       <c r="B28" t="n">
-        <v>91884</v>
+        <v>89252</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3443,25 +3443,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>424010</v>
+        <v>423912</v>
       </c>
       <c r="R28" t="n">
-        <v>6919840</v>
+        <v>6920047</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119830764</v>
+        <v>119830755</v>
       </c>
       <c r="B29" t="n">
-        <v>90582</v>
+        <v>91828</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3549,25 +3549,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>149</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424000</v>
+        <v>424017</v>
       </c>
       <c r="R29" t="n">
-        <v>6919867</v>
+        <v>6919755</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119830759</v>
+        <v>119830734</v>
       </c>
       <c r="B4" t="n">
         <v>91834</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423934</v>
+        <v>423957</v>
       </c>
       <c r="R4" t="n">
-        <v>6920034</v>
+        <v>6919904</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119830734</v>
+        <v>119830759</v>
       </c>
       <c r="B5" t="n">
         <v>91834</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423957</v>
+        <v>423934</v>
       </c>
       <c r="R5" t="n">
-        <v>6919904</v>
+        <v>6920034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119830756</v>
+        <v>119830768</v>
       </c>
       <c r="B2" t="n">
-        <v>91863</v>
+        <v>89252</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>6276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424010</v>
+        <v>423899</v>
       </c>
       <c r="R2" t="n">
-        <v>6919761</v>
+        <v>6920037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119830736</v>
+        <v>119830762</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423894</v>
+        <v>424025</v>
       </c>
       <c r="R3" t="n">
-        <v>6920052</v>
+        <v>6919826</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119830734</v>
+        <v>119830738</v>
       </c>
       <c r="B4" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423957</v>
+        <v>423951</v>
       </c>
       <c r="R4" t="n">
         <v>6919904</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119830759</v>
+        <v>119830736</v>
       </c>
       <c r="B5" t="n">
         <v>91834</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423934</v>
+        <v>423894</v>
       </c>
       <c r="R5" t="n">
-        <v>6920034</v>
+        <v>6920052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119830763</v>
+        <v>119830754</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>424010</v>
+        <v>424024</v>
       </c>
       <c r="R6" t="n">
-        <v>6919840</v>
+        <v>6919740</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119830764</v>
+        <v>119830752</v>
       </c>
       <c r="B7" t="n">
-        <v>90582</v>
+        <v>88153</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>4962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>424000</v>
+        <v>424027</v>
       </c>
       <c r="R7" t="n">
-        <v>6919867</v>
+        <v>6919739</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119830733</v>
+        <v>119830756</v>
       </c>
       <c r="B8" t="n">
-        <v>89252</v>
+        <v>91863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6276</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>423939</v>
+        <v>424010</v>
       </c>
       <c r="R8" t="n">
-        <v>6919929</v>
+        <v>6919761</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119830765</v>
+        <v>119830739</v>
       </c>
       <c r="B10" t="n">
         <v>91834</v>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>424019</v>
+        <v>423961</v>
       </c>
       <c r="R10" t="n">
-        <v>6919898</v>
+        <v>6919906</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119830766</v>
+        <v>119830735</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>423930</v>
+        <v>424039</v>
       </c>
       <c r="R11" t="n">
-        <v>6920043</v>
+        <v>6919773</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119830754</v>
+        <v>119830763</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>424024</v>
+        <v>424010</v>
       </c>
       <c r="R12" t="n">
-        <v>6919740</v>
+        <v>6919840</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119830735</v>
+        <v>119830743</v>
       </c>
       <c r="B13" t="n">
-        <v>89252</v>
+        <v>90067</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6276</v>
+        <v>256703</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>424039</v>
+        <v>424092</v>
       </c>
       <c r="R13" t="n">
-        <v>6919773</v>
+        <v>6919785</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119830767</v>
+        <v>119830733</v>
       </c>
       <c r="B14" t="n">
-        <v>89275</v>
+        <v>89252</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>423917</v>
+        <v>423939</v>
       </c>
       <c r="R14" t="n">
-        <v>6920047</v>
+        <v>6919929</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119830743</v>
+        <v>119830744</v>
       </c>
       <c r="B15" t="n">
-        <v>90067</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>424092</v>
+        <v>424066</v>
       </c>
       <c r="R15" t="n">
-        <v>6919785</v>
+        <v>6919837</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119830744</v>
+        <v>119830771</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>424066</v>
+        <v>423911</v>
       </c>
       <c r="R16" t="n">
-        <v>6919837</v>
+        <v>6920075</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119830738</v>
+        <v>119830751</v>
       </c>
       <c r="B17" t="n">
         <v>91852</v>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>423951</v>
+        <v>424052</v>
       </c>
       <c r="R17" t="n">
-        <v>6919904</v>
+        <v>6919686</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119830739</v>
+        <v>119830737</v>
       </c>
       <c r="B18" t="n">
         <v>91834</v>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>423961</v>
+        <v>423946</v>
       </c>
       <c r="R18" t="n">
-        <v>6919906</v>
+        <v>6919903</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119830752</v>
+        <v>119830753</v>
       </c>
       <c r="B19" t="n">
-        <v>88153</v>
+        <v>91863</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4962</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119830762</v>
+        <v>119830770</v>
       </c>
       <c r="B20" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>424025</v>
+        <v>423909</v>
       </c>
       <c r="R20" t="n">
-        <v>6919826</v>
+        <v>6920068</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119830751</v>
+        <v>119830767</v>
       </c>
       <c r="B21" t="n">
-        <v>91852</v>
+        <v>89275</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2701,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>6286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>424052</v>
+        <v>423917</v>
       </c>
       <c r="R21" t="n">
-        <v>6919686</v>
+        <v>6920047</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830761</v>
+        <v>119830766</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>424024</v>
+        <v>423930</v>
       </c>
       <c r="R22" t="n">
-        <v>6919805</v>
+        <v>6920043</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830737</v>
+        <v>119830761</v>
       </c>
       <c r="B23" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2913,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>423946</v>
+        <v>424024</v>
       </c>
       <c r="R23" t="n">
-        <v>6919903</v>
+        <v>6919805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119830770</v>
+        <v>119830769</v>
       </c>
       <c r="B24" t="n">
-        <v>91832</v>
+        <v>89252</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,25 +3019,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>423909</v>
+        <v>423912</v>
       </c>
       <c r="R24" t="n">
-        <v>6920068</v>
+        <v>6920047</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119830768</v>
+        <v>119830765</v>
       </c>
       <c r="B25" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3125,25 +3125,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>423899</v>
+        <v>424019</v>
       </c>
       <c r="R25" t="n">
-        <v>6920037</v>
+        <v>6919898</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119830753</v>
+        <v>119830734</v>
       </c>
       <c r="B26" t="n">
-        <v>91863</v>
+        <v>91834</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,21 +3235,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>424027</v>
+        <v>423957</v>
       </c>
       <c r="R26" t="n">
-        <v>6919739</v>
+        <v>6919904</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119830771</v>
+        <v>119830755</v>
       </c>
       <c r="B27" t="n">
-        <v>91834</v>
+        <v>91828</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3337,25 +3337,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>423911</v>
+        <v>424017</v>
       </c>
       <c r="R27" t="n">
-        <v>6920075</v>
+        <v>6919755</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119830769</v>
+        <v>119830759</v>
       </c>
       <c r="B28" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3443,25 +3443,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>423912</v>
+        <v>423934</v>
       </c>
       <c r="R28" t="n">
-        <v>6920047</v>
+        <v>6920034</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119830755</v>
+        <v>119830764</v>
       </c>
       <c r="B29" t="n">
-        <v>91828</v>
+        <v>90582</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3549,25 +3549,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>149</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424017</v>
+        <v>424000</v>
       </c>
       <c r="R29" t="n">
-        <v>6919755</v>
+        <v>6919867</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119830768</v>
+        <v>119830762</v>
       </c>
       <c r="B2" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>423899</v>
+        <v>424025</v>
       </c>
       <c r="R2" t="n">
-        <v>6920037</v>
+        <v>6919826</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119830762</v>
+        <v>119830768</v>
       </c>
       <c r="B3" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424025</v>
+        <v>423899</v>
       </c>
       <c r="R3" t="n">
-        <v>6919826</v>
+        <v>6920037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119830739</v>
+        <v>119830743</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>90067</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>423961</v>
+        <v>424092</v>
       </c>
       <c r="R10" t="n">
-        <v>6919906</v>
+        <v>6919785</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119830735</v>
+        <v>119830739</v>
       </c>
       <c r="B11" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>424039</v>
+        <v>423961</v>
       </c>
       <c r="R11" t="n">
-        <v>6919773</v>
+        <v>6919906</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119830763</v>
+        <v>119830735</v>
       </c>
       <c r="B12" t="n">
-        <v>91884</v>
+        <v>89252</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>424010</v>
+        <v>424039</v>
       </c>
       <c r="R12" t="n">
-        <v>6919840</v>
+        <v>6919773</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119830743</v>
+        <v>119830763</v>
       </c>
       <c r="B13" t="n">
-        <v>90067</v>
+        <v>91884</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>256703</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>424092</v>
+        <v>424010</v>
       </c>
       <c r="R13" t="n">
-        <v>6919785</v>
+        <v>6919840</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119830767</v>
+        <v>119830766</v>
       </c>
       <c r="B21" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2701,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423917</v>
+        <v>423930</v>
       </c>
       <c r="R21" t="n">
-        <v>6920047</v>
+        <v>6920043</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830766</v>
+        <v>119830761</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423930</v>
+        <v>424024</v>
       </c>
       <c r="R22" t="n">
-        <v>6920043</v>
+        <v>6919805</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830761</v>
+        <v>119830767</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2913,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>424024</v>
+        <v>423917</v>
       </c>
       <c r="R23" t="n">
-        <v>6919805</v>
+        <v>6920047</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119830762</v>
+        <v>119830768</v>
       </c>
       <c r="B2" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424025</v>
+        <v>423899</v>
       </c>
       <c r="R2" t="n">
-        <v>6919826</v>
+        <v>6920037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119830768</v>
+        <v>119830762</v>
       </c>
       <c r="B3" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423899</v>
+        <v>424025</v>
       </c>
       <c r="R3" t="n">
-        <v>6920037</v>
+        <v>6919826</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119830743</v>
+        <v>119830739</v>
       </c>
       <c r="B10" t="n">
-        <v>90067</v>
+        <v>91834</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>424092</v>
+        <v>423961</v>
       </c>
       <c r="R10" t="n">
-        <v>6919785</v>
+        <v>6919906</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119830739</v>
+        <v>119830743</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>90067</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>423961</v>
+        <v>424092</v>
       </c>
       <c r="R11" t="n">
-        <v>6919906</v>
+        <v>6919785</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119830766</v>
+        <v>119830767</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>89275</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2701,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423930</v>
+        <v>423917</v>
       </c>
       <c r="R21" t="n">
-        <v>6920043</v>
+        <v>6920047</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830761</v>
+        <v>119830766</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>424024</v>
+        <v>423930</v>
       </c>
       <c r="R22" t="n">
-        <v>6919805</v>
+        <v>6920043</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830767</v>
+        <v>119830761</v>
       </c>
       <c r="B23" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2913,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>423917</v>
+        <v>424024</v>
       </c>
       <c r="R23" t="n">
-        <v>6920047</v>
+        <v>6919805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119830768</v>
+        <v>119830762</v>
       </c>
       <c r="B2" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>423899</v>
+        <v>424025</v>
       </c>
       <c r="R2" t="n">
-        <v>6920037</v>
+        <v>6919826</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119830762</v>
+        <v>119830768</v>
       </c>
       <c r="B3" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424025</v>
+        <v>423899</v>
       </c>
       <c r="R3" t="n">
-        <v>6919826</v>
+        <v>6920037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119830767</v>
+        <v>119830766</v>
       </c>
       <c r="B21" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2701,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423917</v>
+        <v>423930</v>
       </c>
       <c r="R21" t="n">
-        <v>6920047</v>
+        <v>6920043</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830766</v>
+        <v>119830761</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423930</v>
+        <v>424024</v>
       </c>
       <c r="R22" t="n">
-        <v>6920043</v>
+        <v>6919805</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830761</v>
+        <v>119830767</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2913,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>424024</v>
+        <v>423917</v>
       </c>
       <c r="R23" t="n">
-        <v>6919805</v>
+        <v>6920047</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119830762</v>
+        <v>119830768</v>
       </c>
       <c r="B2" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424025</v>
+        <v>423899</v>
       </c>
       <c r="R2" t="n">
-        <v>6919826</v>
+        <v>6920037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119830768</v>
+        <v>119830762</v>
       </c>
       <c r="B3" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423899</v>
+        <v>424025</v>
       </c>
       <c r="R3" t="n">
-        <v>6920037</v>
+        <v>6919826</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119830736</v>
+        <v>119830754</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423894</v>
+        <v>424024</v>
       </c>
       <c r="R5" t="n">
-        <v>6920052</v>
+        <v>6919740</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119830754</v>
+        <v>119830736</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>424024</v>
+        <v>423894</v>
       </c>
       <c r="R6" t="n">
-        <v>6919740</v>
+        <v>6920052</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119830739</v>
+        <v>119830743</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>90067</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>423961</v>
+        <v>424092</v>
       </c>
       <c r="R10" t="n">
-        <v>6919906</v>
+        <v>6919785</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119830743</v>
+        <v>119830739</v>
       </c>
       <c r="B11" t="n">
-        <v>90067</v>
+        <v>91834</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>424092</v>
+        <v>423961</v>
       </c>
       <c r="R11" t="n">
-        <v>6919785</v>
+        <v>6919906</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119830768</v>
+        <v>119830762</v>
       </c>
       <c r="B2" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>423899</v>
+        <v>424025</v>
       </c>
       <c r="R2" t="n">
-        <v>6920037</v>
+        <v>6919826</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119830762</v>
+        <v>119830768</v>
       </c>
       <c r="B3" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424025</v>
+        <v>423899</v>
       </c>
       <c r="R3" t="n">
-        <v>6919826</v>
+        <v>6920037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119830743</v>
+        <v>119830739</v>
       </c>
       <c r="B10" t="n">
-        <v>90067</v>
+        <v>91834</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>424092</v>
+        <v>423961</v>
       </c>
       <c r="R10" t="n">
-        <v>6919785</v>
+        <v>6919906</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119830739</v>
+        <v>119830743</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>90067</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>423961</v>
+        <v>424092</v>
       </c>
       <c r="R11" t="n">
-        <v>6919906</v>
+        <v>6919785</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119830762</v>
+        <v>119830754</v>
       </c>
       <c r="B2" t="n">
-        <v>91856</v>
+        <v>91850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424025</v>
+        <v>424024</v>
       </c>
       <c r="R2" t="n">
-        <v>6919826</v>
+        <v>6919740</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119830768</v>
+        <v>119830755</v>
       </c>
       <c r="B3" t="n">
-        <v>89252</v>
+        <v>91846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>149</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423899</v>
+        <v>424017</v>
       </c>
       <c r="R3" t="n">
-        <v>6920037</v>
+        <v>6919755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119830738</v>
+        <v>119830759</v>
       </c>
       <c r="B4" t="n">
         <v>91852</v>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423951</v>
+        <v>423934</v>
       </c>
       <c r="R4" t="n">
-        <v>6919904</v>
+        <v>6920034</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119830754</v>
+        <v>119830770</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>424024</v>
+        <v>423909</v>
       </c>
       <c r="R5" t="n">
-        <v>6919740</v>
+        <v>6920068</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119830736</v>
+        <v>119830768</v>
       </c>
       <c r="B6" t="n">
-        <v>91834</v>
+        <v>89269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>423894</v>
+        <v>423899</v>
       </c>
       <c r="R6" t="n">
-        <v>6920052</v>
+        <v>6920037</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119830752</v>
+        <v>119830769</v>
       </c>
       <c r="B7" t="n">
-        <v>88153</v>
+        <v>89269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4962</v>
+        <v>6276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>424027</v>
+        <v>423912</v>
       </c>
       <c r="R7" t="n">
-        <v>6919739</v>
+        <v>6920047</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119830756</v>
+        <v>119830738</v>
       </c>
       <c r="B8" t="n">
-        <v>91863</v>
+        <v>91870</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>424010</v>
+        <v>423951</v>
       </c>
       <c r="R8" t="n">
-        <v>6919761</v>
+        <v>6919904</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119830760</v>
+        <v>119830764</v>
       </c>
       <c r="B9" t="n">
-        <v>89252</v>
+        <v>90600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6276</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>424023</v>
+        <v>424000</v>
       </c>
       <c r="R9" t="n">
-        <v>6919928</v>
+        <v>6919867</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119830739</v>
+        <v>119830753</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>91881</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>423961</v>
+        <v>424027</v>
       </c>
       <c r="R10" t="n">
-        <v>6919906</v>
+        <v>6919739</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119830743</v>
+        <v>119830766</v>
       </c>
       <c r="B11" t="n">
-        <v>90067</v>
+        <v>91852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>424092</v>
+        <v>423930</v>
       </c>
       <c r="R11" t="n">
-        <v>6919785</v>
+        <v>6920043</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119830735</v>
+        <v>119830737</v>
       </c>
       <c r="B12" t="n">
-        <v>89252</v>
+        <v>91852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>424039</v>
+        <v>423946</v>
       </c>
       <c r="R12" t="n">
-        <v>6919773</v>
+        <v>6919903</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119830763</v>
+        <v>119830739</v>
       </c>
       <c r="B13" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>424010</v>
+        <v>423961</v>
       </c>
       <c r="R13" t="n">
-        <v>6919840</v>
+        <v>6919906</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119830733</v>
+        <v>119830763</v>
       </c>
       <c r="B14" t="n">
-        <v>89252</v>
+        <v>91902</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>423939</v>
+        <v>424010</v>
       </c>
       <c r="R14" t="n">
-        <v>6919929</v>
+        <v>6919840</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119830744</v>
+        <v>119830743</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>90084</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>424066</v>
+        <v>424092</v>
       </c>
       <c r="R15" t="n">
-        <v>6919837</v>
+        <v>6919785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119830771</v>
+        <v>119830736</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>423911</v>
+        <v>423894</v>
       </c>
       <c r="R16" t="n">
-        <v>6920075</v>
+        <v>6920052</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
         <v>119830751</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119830737</v>
+        <v>119830761</v>
       </c>
       <c r="B18" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>423946</v>
+        <v>424024</v>
       </c>
       <c r="R18" t="n">
-        <v>6919903</v>
+        <v>6919805</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119830753</v>
+        <v>119830744</v>
       </c>
       <c r="B19" t="n">
-        <v>91863</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>424027</v>
+        <v>424066</v>
       </c>
       <c r="R19" t="n">
-        <v>6919739</v>
+        <v>6919837</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119830770</v>
+        <v>119830767</v>
       </c>
       <c r="B20" t="n">
-        <v>91832</v>
+        <v>89292</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423909</v>
+        <v>423917</v>
       </c>
       <c r="R20" t="n">
-        <v>6920068</v>
+        <v>6920047</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119830766</v>
+        <v>119830752</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>88170</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4962</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423930</v>
+        <v>424027</v>
       </c>
       <c r="R21" t="n">
-        <v>6920043</v>
+        <v>6919739</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830761</v>
+        <v>119830733</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>89269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>424024</v>
+        <v>423939</v>
       </c>
       <c r="R22" t="n">
-        <v>6919805</v>
+        <v>6919929</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830767</v>
+        <v>119830735</v>
       </c>
       <c r="B23" t="n">
-        <v>89275</v>
+        <v>89269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>423917</v>
+        <v>424039</v>
       </c>
       <c r="R23" t="n">
-        <v>6920047</v>
+        <v>6919773</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119830769</v>
+        <v>119830771</v>
       </c>
       <c r="B24" t="n">
-        <v>89252</v>
+        <v>91852</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,25 +3019,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>423912</v>
+        <v>423911</v>
       </c>
       <c r="R24" t="n">
-        <v>6920047</v>
+        <v>6920075</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3116,7 +3116,7 @@
         <v>119830765</v>
       </c>
       <c r="B25" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119830734</v>
+        <v>119830756</v>
       </c>
       <c r="B26" t="n">
-        <v>91834</v>
+        <v>91881</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,21 +3235,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>423957</v>
+        <v>424010</v>
       </c>
       <c r="R26" t="n">
-        <v>6919904</v>
+        <v>6919761</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119830755</v>
+        <v>119830760</v>
       </c>
       <c r="B27" t="n">
-        <v>91828</v>
+        <v>89269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>149</v>
+        <v>6276</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>424017</v>
+        <v>424023</v>
       </c>
       <c r="R27" t="n">
-        <v>6919755</v>
+        <v>6919928</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119830759</v>
+        <v>119830762</v>
       </c>
       <c r="B28" t="n">
-        <v>91834</v>
+        <v>91874</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,21 +3447,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>423934</v>
+        <v>424025</v>
       </c>
       <c r="R28" t="n">
-        <v>6920034</v>
+        <v>6919826</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119830764</v>
+        <v>119830734</v>
       </c>
       <c r="B29" t="n">
-        <v>90582</v>
+        <v>91852</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3553,21 +3553,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424000</v>
+        <v>423957</v>
       </c>
       <c r="R29" t="n">
-        <v>6919867</v>
+        <v>6919904</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119830737</v>
+        <v>119830763</v>
       </c>
       <c r="B12" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>423946</v>
+        <v>424010</v>
       </c>
       <c r="R12" t="n">
-        <v>6919903</v>
+        <v>6919840</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119830739</v>
+        <v>119830737</v>
       </c>
       <c r="B13" t="n">
         <v>91852</v>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>423961</v>
+        <v>423946</v>
       </c>
       <c r="R13" t="n">
-        <v>6919906</v>
+        <v>6919903</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119830763</v>
+        <v>119830739</v>
       </c>
       <c r="B14" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>424010</v>
+        <v>423961</v>
       </c>
       <c r="R14" t="n">
-        <v>6919840</v>
+        <v>6919906</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119830754</v>
+        <v>119830752</v>
       </c>
       <c r="B2" t="n">
-        <v>91850</v>
+        <v>88170</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424024</v>
+        <v>424027</v>
       </c>
       <c r="R2" t="n">
-        <v>6919740</v>
+        <v>6919739</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119830755</v>
+        <v>119830769</v>
       </c>
       <c r="B3" t="n">
-        <v>91846</v>
+        <v>89269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>149</v>
+        <v>6276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424017</v>
+        <v>423912</v>
       </c>
       <c r="R3" t="n">
-        <v>6919755</v>
+        <v>6920047</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119830759</v>
+        <v>119830755</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>91846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423934</v>
+        <v>424017</v>
       </c>
       <c r="R4" t="n">
-        <v>6920034</v>
+        <v>6919755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119830770</v>
+        <v>119830737</v>
       </c>
       <c r="B5" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423909</v>
+        <v>423946</v>
       </c>
       <c r="R5" t="n">
-        <v>6920068</v>
+        <v>6919903</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119830768</v>
+        <v>119830763</v>
       </c>
       <c r="B6" t="n">
-        <v>89269</v>
+        <v>91902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>423899</v>
+        <v>424010</v>
       </c>
       <c r="R6" t="n">
-        <v>6920037</v>
+        <v>6919840</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119830769</v>
+        <v>119830756</v>
       </c>
       <c r="B7" t="n">
-        <v>89269</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>423912</v>
+        <v>424010</v>
       </c>
       <c r="R7" t="n">
-        <v>6920047</v>
+        <v>6919761</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119830738</v>
+        <v>119830744</v>
       </c>
       <c r="B8" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>423951</v>
+        <v>424066</v>
       </c>
       <c r="R8" t="n">
-        <v>6919904</v>
+        <v>6919837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119830764</v>
+        <v>119830733</v>
       </c>
       <c r="B9" t="n">
-        <v>90600</v>
+        <v>89269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>424000</v>
+        <v>423939</v>
       </c>
       <c r="R9" t="n">
-        <v>6919867</v>
+        <v>6919929</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119830753</v>
+        <v>119830761</v>
       </c>
       <c r="B10" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>424027</v>
+        <v>424024</v>
       </c>
       <c r="R10" t="n">
-        <v>6919739</v>
+        <v>6919805</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119830766</v>
+        <v>119830753</v>
       </c>
       <c r="B11" t="n">
-        <v>91852</v>
+        <v>91881</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>423930</v>
+        <v>424027</v>
       </c>
       <c r="R11" t="n">
-        <v>6920043</v>
+        <v>6919739</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119830763</v>
+        <v>119830754</v>
       </c>
       <c r="B12" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>424010</v>
+        <v>424024</v>
       </c>
       <c r="R12" t="n">
-        <v>6919840</v>
+        <v>6919740</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119830737</v>
+        <v>119830743</v>
       </c>
       <c r="B13" t="n">
-        <v>91852</v>
+        <v>90084</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>423946</v>
+        <v>424092</v>
       </c>
       <c r="R13" t="n">
-        <v>6919903</v>
+        <v>6919785</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119830739</v>
+        <v>119830764</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
+        <v>90600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>423961</v>
+        <v>424000</v>
       </c>
       <c r="R14" t="n">
-        <v>6919906</v>
+        <v>6919867</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119830743</v>
+        <v>119830751</v>
       </c>
       <c r="B15" t="n">
-        <v>90084</v>
+        <v>91870</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>256703</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>424092</v>
+        <v>424052</v>
       </c>
       <c r="R15" t="n">
-        <v>6919785</v>
+        <v>6919686</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119830736</v>
+        <v>119830739</v>
       </c>
       <c r="B16" t="n">
         <v>91852</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>423894</v>
+        <v>423961</v>
       </c>
       <c r="R16" t="n">
-        <v>6920052</v>
+        <v>6919906</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119830751</v>
+        <v>119830771</v>
       </c>
       <c r="B17" t="n">
-        <v>91870</v>
+        <v>91852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>424052</v>
+        <v>423911</v>
       </c>
       <c r="R17" t="n">
-        <v>6919686</v>
+        <v>6920075</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119830761</v>
+        <v>119830765</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>424024</v>
+        <v>424019</v>
       </c>
       <c r="R18" t="n">
-        <v>6919805</v>
+        <v>6919898</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119830744</v>
+        <v>119830735</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>89269</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>424066</v>
+        <v>424039</v>
       </c>
       <c r="R19" t="n">
-        <v>6919837</v>
+        <v>6919773</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119830767</v>
+        <v>119830766</v>
       </c>
       <c r="B20" t="n">
-        <v>89292</v>
+        <v>91852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423917</v>
+        <v>423930</v>
       </c>
       <c r="R20" t="n">
-        <v>6920047</v>
+        <v>6920043</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119830752</v>
+        <v>119830770</v>
       </c>
       <c r="B21" t="n">
-        <v>88170</v>
+        <v>91850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4962</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>424027</v>
+        <v>423909</v>
       </c>
       <c r="R21" t="n">
-        <v>6919739</v>
+        <v>6920068</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830733</v>
+        <v>119830768</v>
       </c>
       <c r="B22" t="n">
         <v>89269</v>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423939</v>
+        <v>423899</v>
       </c>
       <c r="R22" t="n">
-        <v>6919929</v>
+        <v>6920037</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,7 +2901,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830735</v>
+        <v>119830760</v>
       </c>
       <c r="B23" t="n">
         <v>89269</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>424039</v>
+        <v>424023</v>
       </c>
       <c r="R23" t="n">
-        <v>6919773</v>
+        <v>6919928</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119830771</v>
+        <v>119830738</v>
       </c>
       <c r="B24" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,25 +3019,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>423911</v>
+        <v>423951</v>
       </c>
       <c r="R24" t="n">
-        <v>6920075</v>
+        <v>6919904</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119830765</v>
+        <v>119830759</v>
       </c>
       <c r="B25" t="n">
         <v>91852</v>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>424019</v>
+        <v>423934</v>
       </c>
       <c r="R25" t="n">
-        <v>6919898</v>
+        <v>6920034</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119830756</v>
+        <v>119830762</v>
       </c>
       <c r="B26" t="n">
-        <v>91881</v>
+        <v>91874</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,21 +3235,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>424010</v>
+        <v>424025</v>
       </c>
       <c r="R26" t="n">
-        <v>6919761</v>
+        <v>6919826</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119830760</v>
+        <v>119830767</v>
       </c>
       <c r="B27" t="n">
-        <v>89269</v>
+        <v>89292</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6276</v>
+        <v>6286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>424023</v>
+        <v>423917</v>
       </c>
       <c r="R27" t="n">
-        <v>6919928</v>
+        <v>6920047</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119830762</v>
+        <v>119830734</v>
       </c>
       <c r="B28" t="n">
-        <v>91874</v>
+        <v>91852</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,21 +3447,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>424025</v>
+        <v>423957</v>
       </c>
       <c r="R28" t="n">
-        <v>6919826</v>
+        <v>6919904</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,7 +3537,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119830734</v>
+        <v>119830736</v>
       </c>
       <c r="B29" t="n">
         <v>91852</v>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>423957</v>
+        <v>423894</v>
       </c>
       <c r="R29" t="n">
-        <v>6919904</v>
+        <v>6920052</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119830769</v>
+        <v>119830763</v>
       </c>
       <c r="B3" t="n">
-        <v>89269</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423912</v>
+        <v>424010</v>
       </c>
       <c r="R3" t="n">
-        <v>6920047</v>
+        <v>6919840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119830755</v>
+        <v>119830737</v>
       </c>
       <c r="B4" t="n">
-        <v>91846</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>424017</v>
+        <v>423946</v>
       </c>
       <c r="R4" t="n">
-        <v>6919755</v>
+        <v>6919903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119830737</v>
+        <v>119830769</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>89269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423946</v>
+        <v>423912</v>
       </c>
       <c r="R5" t="n">
-        <v>6919903</v>
+        <v>6920047</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119830763</v>
+        <v>119830755</v>
       </c>
       <c r="B6" t="n">
-        <v>91902</v>
+        <v>91846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>149</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>424010</v>
+        <v>424017</v>
       </c>
       <c r="R6" t="n">
-        <v>6919840</v>
+        <v>6919755</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119830771</v>
+        <v>119830765</v>
       </c>
       <c r="B17" t="n">
         <v>91852</v>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>423911</v>
+        <v>424019</v>
       </c>
       <c r="R17" t="n">
-        <v>6920075</v>
+        <v>6919898</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119830765</v>
+        <v>119830771</v>
       </c>
       <c r="B18" t="n">
         <v>91852</v>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>424019</v>
+        <v>423911</v>
       </c>
       <c r="R18" t="n">
-        <v>6919898</v>
+        <v>6920075</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119830752</v>
+        <v>119830739</v>
       </c>
       <c r="B2" t="n">
-        <v>88170</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4962</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424027</v>
+        <v>423961</v>
       </c>
       <c r="R2" t="n">
-        <v>6919739</v>
+        <v>6919906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119830763</v>
+        <v>119830766</v>
       </c>
       <c r="B3" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424010</v>
+        <v>423930</v>
       </c>
       <c r="R3" t="n">
-        <v>6919840</v>
+        <v>6920043</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119830737</v>
+        <v>119830752</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>88170</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423946</v>
+        <v>424027</v>
       </c>
       <c r="R4" t="n">
-        <v>6919903</v>
+        <v>6919739</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119830769</v>
+        <v>119830743</v>
       </c>
       <c r="B5" t="n">
-        <v>89269</v>
+        <v>90084</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>256703</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423912</v>
+        <v>424092</v>
       </c>
       <c r="R5" t="n">
-        <v>6920047</v>
+        <v>6919785</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119830755</v>
+        <v>119830736</v>
       </c>
       <c r="B6" t="n">
-        <v>91846</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>424017</v>
+        <v>423894</v>
       </c>
       <c r="R6" t="n">
-        <v>6919755</v>
+        <v>6920052</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119830756</v>
+        <v>119830759</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>91852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>424010</v>
+        <v>423934</v>
       </c>
       <c r="R7" t="n">
-        <v>6919761</v>
+        <v>6920034</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119830744</v>
+        <v>119830769</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>89269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>424066</v>
+        <v>423912</v>
       </c>
       <c r="R8" t="n">
-        <v>6919837</v>
+        <v>6920047</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119830733</v>
+        <v>119830767</v>
       </c>
       <c r="B9" t="n">
-        <v>89269</v>
+        <v>89292</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6276</v>
+        <v>6286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>423939</v>
+        <v>423917</v>
       </c>
       <c r="R9" t="n">
-        <v>6919929</v>
+        <v>6920047</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119830761</v>
+        <v>119830765</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>424024</v>
+        <v>424019</v>
       </c>
       <c r="R10" t="n">
-        <v>6919805</v>
+        <v>6919898</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119830753</v>
+        <v>119830770</v>
       </c>
       <c r="B11" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>424027</v>
+        <v>423909</v>
       </c>
       <c r="R11" t="n">
-        <v>6919739</v>
+        <v>6920068</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119830754</v>
+        <v>119830756</v>
       </c>
       <c r="B12" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>424024</v>
+        <v>424010</v>
       </c>
       <c r="R12" t="n">
-        <v>6919740</v>
+        <v>6919761</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119830743</v>
+        <v>119830753</v>
       </c>
       <c r="B13" t="n">
-        <v>90084</v>
+        <v>91881</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>424092</v>
+        <v>424027</v>
       </c>
       <c r="R13" t="n">
-        <v>6919785</v>
+        <v>6919739</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119830751</v>
+        <v>119830735</v>
       </c>
       <c r="B15" t="n">
-        <v>91870</v>
+        <v>89269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>424052</v>
+        <v>424039</v>
       </c>
       <c r="R15" t="n">
-        <v>6919686</v>
+        <v>6919773</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119830739</v>
+        <v>119830762</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>423961</v>
+        <v>424025</v>
       </c>
       <c r="R16" t="n">
-        <v>6919906</v>
+        <v>6919826</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119830765</v>
+        <v>119830738</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>424019</v>
+        <v>423951</v>
       </c>
       <c r="R17" t="n">
-        <v>6919898</v>
+        <v>6919904</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119830771</v>
+        <v>119830768</v>
       </c>
       <c r="B18" t="n">
-        <v>91852</v>
+        <v>89269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>423911</v>
+        <v>423899</v>
       </c>
       <c r="R18" t="n">
-        <v>6920075</v>
+        <v>6920037</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119830735</v>
+        <v>119830760</v>
       </c>
       <c r="B19" t="n">
         <v>89269</v>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>424039</v>
+        <v>424023</v>
       </c>
       <c r="R19" t="n">
-        <v>6919773</v>
+        <v>6919928</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119830766</v>
+        <v>119830734</v>
       </c>
       <c r="B20" t="n">
         <v>91852</v>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423930</v>
+        <v>423957</v>
       </c>
       <c r="R20" t="n">
-        <v>6920043</v>
+        <v>6919904</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119830770</v>
+        <v>119830733</v>
       </c>
       <c r="B21" t="n">
-        <v>91850</v>
+        <v>89269</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2701,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423909</v>
+        <v>423939</v>
       </c>
       <c r="R21" t="n">
-        <v>6920068</v>
+        <v>6919929</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830768</v>
+        <v>119830754</v>
       </c>
       <c r="B22" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423899</v>
+        <v>424024</v>
       </c>
       <c r="R22" t="n">
-        <v>6920037</v>
+        <v>6919740</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830760</v>
+        <v>119830761</v>
       </c>
       <c r="B23" t="n">
-        <v>89269</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2913,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>424023</v>
+        <v>424024</v>
       </c>
       <c r="R23" t="n">
-        <v>6919928</v>
+        <v>6919805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119830738</v>
+        <v>119830763</v>
       </c>
       <c r="B24" t="n">
-        <v>91870</v>
+        <v>91902</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,25 +3019,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>423951</v>
+        <v>424010</v>
       </c>
       <c r="R24" t="n">
-        <v>6919904</v>
+        <v>6919840</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119830759</v>
+        <v>119830771</v>
       </c>
       <c r="B25" t="n">
         <v>91852</v>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>423934</v>
+        <v>423911</v>
       </c>
       <c r="R25" t="n">
-        <v>6920034</v>
+        <v>6920075</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119830762</v>
+        <v>119830755</v>
       </c>
       <c r="B26" t="n">
-        <v>91874</v>
+        <v>91846</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>424025</v>
+        <v>424017</v>
       </c>
       <c r="R26" t="n">
-        <v>6919826</v>
+        <v>6919755</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119830767</v>
+        <v>119830737</v>
       </c>
       <c r="B27" t="n">
-        <v>89292</v>
+        <v>91852</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3337,25 +3337,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>423917</v>
+        <v>423946</v>
       </c>
       <c r="R27" t="n">
-        <v>6920047</v>
+        <v>6919903</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119830734</v>
+        <v>119830751</v>
       </c>
       <c r="B28" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3443,25 +3443,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>423957</v>
+        <v>424052</v>
       </c>
       <c r="R28" t="n">
-        <v>6919904</v>
+        <v>6919686</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119830736</v>
+        <v>119830744</v>
       </c>
       <c r="B29" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3549,25 +3549,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>423894</v>
+        <v>424066</v>
       </c>
       <c r="R29" t="n">
-        <v>6920052</v>
+        <v>6919837</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119830733</v>
+        <v>119830754</v>
       </c>
       <c r="B21" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2701,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>423939</v>
+        <v>424024</v>
       </c>
       <c r="R21" t="n">
-        <v>6919929</v>
+        <v>6919740</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830754</v>
+        <v>119830733</v>
       </c>
       <c r="B22" t="n">
-        <v>91850</v>
+        <v>89269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>424024</v>
+        <v>423939</v>
       </c>
       <c r="R22" t="n">
-        <v>6919740</v>
+        <v>6919929</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119830739</v>
+        <v>119830755</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>423961</v>
+        <v>424017</v>
       </c>
       <c r="R2" t="n">
-        <v>6919906</v>
+        <v>6919755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,50 +776,56 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119830766</v>
+        <v>504690</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>1853</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandbarrskog öster om Haraldsåsen, Hjd</t>
+          <t>Remmet / 2 km NV /, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423930</v>
+        <v>424105</v>
       </c>
       <c r="R3" t="n">
-        <v>6920043</v>
+        <v>6919768</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,14 +850,24 @@
           <t>Hede</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Z-Här-0638</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2005-05-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2005-05-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 ex. varav 1 bl. i relativt lavrik tallskog vid 1382460/ 6923115. Endast återfunnen på denna. Totalt uppgifter från Svea och Evert Amundsson om 7 växtplatser inom ca 1 km sträcka mellan Kvarnån och kraftledningsgata (1382465/ 6923304 till 1382797/ 6922524 NV - SO).</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,53 +882,48 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Z Län Floraväktarna</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg, Rashid Kadhim</t>
+          <t>Lisa Öberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119830752</v>
+        <v>119830758</v>
       </c>
       <c r="B4" t="n">
-        <v>88170</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4962</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>424027</v>
+        <v>424043</v>
       </c>
       <c r="R4" t="n">
-        <v>6919739</v>
+        <v>6919913</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,37 +999,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119830743</v>
+        <v>119830762</v>
       </c>
       <c r="B5" t="n">
-        <v>90084</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>256703</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>424092</v>
+        <v>424025</v>
       </c>
       <c r="R5" t="n">
-        <v>6919785</v>
+        <v>6919826</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,15 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119830736</v>
+        <v>119830754</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1111,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>423894</v>
+        <v>424024</v>
       </c>
       <c r="R6" t="n">
-        <v>6920052</v>
+        <v>6919740</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,15 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119830759</v>
+        <v>119830770</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1212,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>423934</v>
+        <v>423909</v>
       </c>
       <c r="R7" t="n">
-        <v>6920034</v>
+        <v>6920068</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,37 +1302,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119830769</v>
+        <v>119830734</v>
       </c>
       <c r="B8" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>423912</v>
+        <v>423957</v>
       </c>
       <c r="R8" t="n">
-        <v>6920047</v>
+        <v>6919904</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,37 +1403,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119830767</v>
+        <v>119830736</v>
       </c>
       <c r="B9" t="n">
-        <v>89292</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>423917</v>
+        <v>423894</v>
       </c>
       <c r="R9" t="n">
-        <v>6920047</v>
+        <v>6920052</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,15 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119830765</v>
+        <v>119830737</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>424019</v>
+        <v>423946</v>
       </c>
       <c r="R10" t="n">
-        <v>6919898</v>
+        <v>6919903</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,15 +1605,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119830770</v>
+        <v>119830739</v>
       </c>
       <c r="B11" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,21 +1616,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>423909</v>
+        <v>423961</v>
       </c>
       <c r="R11" t="n">
-        <v>6920068</v>
+        <v>6919906</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,15 +1706,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119830756</v>
+        <v>119830757</v>
       </c>
       <c r="B12" t="n">
-        <v>91881</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1717,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1741,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>424010</v>
+        <v>424047</v>
       </c>
       <c r="R12" t="n">
-        <v>6919761</v>
+        <v>6919929</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,15 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119830753</v>
+        <v>119830759</v>
       </c>
       <c r="B13" t="n">
-        <v>91881</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>424027</v>
+        <v>423934</v>
       </c>
       <c r="R13" t="n">
-        <v>6919739</v>
+        <v>6920034</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,15 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119830764</v>
+        <v>119830765</v>
       </c>
       <c r="B14" t="n">
-        <v>90600</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1963,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>424000</v>
+        <v>424019</v>
       </c>
       <c r="R14" t="n">
-        <v>6919867</v>
+        <v>6919898</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,37 +2009,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119830735</v>
+        <v>119830766</v>
       </c>
       <c r="B15" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2044,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>424039</v>
+        <v>423930</v>
       </c>
       <c r="R15" t="n">
-        <v>6919773</v>
+        <v>6920043</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,15 +2110,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119830762</v>
+        <v>119830771</v>
       </c>
       <c r="B16" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,21 +2121,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2145,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>424025</v>
+        <v>423911</v>
       </c>
       <c r="R16" t="n">
-        <v>6919826</v>
+        <v>6920075</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,37 +2211,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119830738</v>
+        <v>119830744</v>
       </c>
       <c r="B17" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2246,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>423951</v>
+        <v>424066</v>
       </c>
       <c r="R17" t="n">
-        <v>6919904</v>
+        <v>6919837</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,37 +2312,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119830768</v>
+        <v>119830761</v>
       </c>
       <c r="B18" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>423899</v>
+        <v>424024</v>
       </c>
       <c r="R18" t="n">
-        <v>6920037</v>
+        <v>6919805</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,53 +2413,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119830760</v>
+        <v>119688787</v>
       </c>
       <c r="B19" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandbarrskog öster om Haraldsåsen, Hjd</t>
+          <t>Haraldsåsen, Haraldsåsen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>424023</v>
+        <v>424107</v>
       </c>
       <c r="R19" t="n">
-        <v>6919928</v>
+        <v>6919810</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2550,9 +2481,19 @@
           <t>2024-09-11</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2567,31 +2508,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg, Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
-        </is>
-      </c>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119830734</v>
+        <v>119830738</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,21 +2531,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,7 +2555,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>423957</v>
+        <v>423951</v>
       </c>
       <c r="R20" t="n">
         <v>6919904</v>
@@ -2689,15 +2621,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119830754</v>
+        <v>119830751</v>
       </c>
       <c r="B21" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2705,21 +2632,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>424024</v>
+        <v>424052</v>
       </c>
       <c r="R21" t="n">
-        <v>6919740</v>
+        <v>6919686</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,37 +2722,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830733</v>
+        <v>119830752</v>
       </c>
       <c r="B22" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90522</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6276</v>
+        <v>4962</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>423939</v>
+        <v>424027</v>
       </c>
       <c r="R22" t="n">
-        <v>6919929</v>
+        <v>6919739</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,37 +2823,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830761</v>
+        <v>119830764</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2858,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>424024</v>
+        <v>424000</v>
       </c>
       <c r="R23" t="n">
-        <v>6919805</v>
+        <v>6919867</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,15 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119830763</v>
+        <v>119830753</v>
       </c>
       <c r="B24" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3023,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>424010</v>
+        <v>424027</v>
       </c>
       <c r="R24" t="n">
-        <v>6919840</v>
+        <v>6919739</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,15 +3025,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119830771</v>
+        <v>119830756</v>
       </c>
       <c r="B25" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3129,21 +3036,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3153,10 +3060,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>423911</v>
+        <v>424010</v>
       </c>
       <c r="R25" t="n">
-        <v>6920075</v>
+        <v>6919761</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,15 +3126,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119830755</v>
+        <v>119830733</v>
       </c>
       <c r="B26" t="n">
-        <v>91846</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3235,21 +3137,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>149</v>
+        <v>6276</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3259,10 +3161,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>424017</v>
+        <v>423939</v>
       </c>
       <c r="R26" t="n">
-        <v>6919755</v>
+        <v>6919929</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,37 +3227,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119830737</v>
+        <v>119830735</v>
       </c>
       <c r="B27" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3365,10 +3262,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>423946</v>
+        <v>424039</v>
       </c>
       <c r="R27" t="n">
-        <v>6919903</v>
+        <v>6919773</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,37 +3328,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119830751</v>
+        <v>119830760</v>
       </c>
       <c r="B28" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3471,10 +3363,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>424052</v>
+        <v>424023</v>
       </c>
       <c r="R28" t="n">
-        <v>6919686</v>
+        <v>6919928</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,37 +3429,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119830744</v>
+        <v>119830768</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3577,10 +3464,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424066</v>
+        <v>423899</v>
       </c>
       <c r="R29" t="n">
-        <v>6919837</v>
+        <v>6920037</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3636,6 +3523,309 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>119830769</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sandbarrskog öster om Haraldsåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>423912</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6920047</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg, Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>119830767</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sandbarrskog öster om Haraldsåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>423917</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6920047</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg, Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>119830743</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sandbarrskog öster om Haraldsåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>424092</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6919785</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg, Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>

--- a/artfynd/A 45557-2021 artfynd.xlsx
+++ b/artfynd/A 45557-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830755</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/504690</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830758</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830762</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830754</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830770</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830734</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1501,6 +1541,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830736</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830737</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1703,6 +1753,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830739</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1804,6 +1859,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830757</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1905,6 +1965,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830759</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2006,6 +2071,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830765</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2107,6 +2177,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830766</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2208,6 +2283,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830771</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2309,6 +2389,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830744</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2410,6 +2495,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830761</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2517,6 +2607,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119688787</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2618,6 +2713,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830738</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2719,6 +2819,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830751</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2820,6 +2925,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830752</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2921,6 +3031,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830764</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3022,6 +3137,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830753</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3123,6 +3243,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830756</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3224,6 +3349,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830733</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3325,6 +3455,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830735</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3426,6 +3561,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830760</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3527,6 +3667,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830768</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3628,6 +3773,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830769</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3729,6 +3879,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830767</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3830,8 +3985,46 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830743</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>